--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_334_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_334_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4903</v>
+        <v>6.1637</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2322</v>
+        <v>5.704</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2581</v>
+        <v>0.4598</v>
       </c>
       <c r="G2" t="n">
         <v>5.3658</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6282</v>
+        <v>0.0452</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8215</v>
+        <v>-0.3497</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1933</v>
+        <v>0.3949</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2245</v>
+        <v>0.7065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5059</v>
+        <v>-0.0898</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7186</v>
+        <v>0.7963</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.21</v>
+        <v>-2.6827</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2353</v>
+        <v>0.2017</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4453</v>
+        <v>-2.8844</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4372</v>
+        <v>-1.7218</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1427</v>
+        <v>-0.4166</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2944</v>
+        <v>-1.3051</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6472</v>
+        <v>-0.9609</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0926</v>
+        <v>0.6183</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7398</v>
+        <v>-1.5792</v>
       </c>
       <c r="P3" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7834</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.883</v>
+        <v>0.1573</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2284</v>
+        <v>0.0237</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6546</v>
+        <v>0.1336</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2899</v>
+        <v>0.3407</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2681</v>
+        <v>-0.3353</v>
       </c>
       <c r="G4" t="n">
         <v>1.0177</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5764</v>
+        <v>0.6271</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1845</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7609</v>
+        <v>0.6937</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0341</v>
+        <v>0.3046</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5616</v>
+        <v>2.3249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5274</v>
+        <v>-2.0203</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6827</v>
+        <v>-0.3806</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2017</v>
+        <v>0.6735</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8844</v>
+        <v>-1.054</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7218</v>
+        <v>2.3069</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4166</v>
+        <v>1.0958</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3051</v>
+        <v>1.211</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9609</v>
+        <v>-2.6874</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6183</v>
+        <v>-0.4223</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5792</v>
+        <v>-2.2651</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5834</v>
+        <v>-1.833</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>-1.1084</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1353</v>
+        <v>-0.7246</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6083</v>
+        <v>2.2862</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6083</v>
+        <v>2.2862</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1964</v>
+        <v>0.1881</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7903</v>
+        <v>-0.1272</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9867</v>
+        <v>0.3153</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3806</v>
+        <v>-0.21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6735</v>
+        <v>1.2353</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.054</v>
+        <v>-1.4453</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3069</v>
+        <v>1.4372</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0958</v>
+        <v>1.1427</v>
       </c>
       <c r="L6" t="n">
-        <v>1.211</v>
+        <v>0.2944</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6874</v>
+        <v>-1.6472</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4223</v>
+        <v>0.0926</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2651</v>
+        <v>-1.7398</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.334</v>
+        <v>-0.1533</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.643</v>
+        <v>-0.4046</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6909999999999999</v>
+        <v>0.2513</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2862</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4152</v>
+        <v>-0.5718</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3548</v>
+        <v>0.6851</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.77</v>
+        <v>-1.2568</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6938</v>
+        <v>-0.615</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6278</v>
+        <v>0.0241</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3216</v>
+        <v>-0.6391</v>
       </c>
       <c r="J7" t="n">
-        <v>0.614</v>
+        <v>0.85</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3564</v>
+        <v>0.0672</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2576</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3078</v>
+        <v>-1.4651</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2714</v>
+        <v>-0.0431</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5792</v>
+        <v>-1.422</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3328</v>
+        <v>-0.8845</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9006</v>
+        <v>-0.165</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4323</v>
+        <v>-0.7196</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5764</v>
+        <v>-0.887</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149</v>
+        <v>-0.117</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3913</v>
+        <v>-0.77</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.615</v>
+        <v>-0.6938</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0241</v>
+        <v>0.6278</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6391</v>
+        <v>-1.3216</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0.614</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0672</v>
+        <v>0.3564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.2576</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4651</v>
+        <v>-1.3078</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0431</v>
+        <v>0.2714</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.422</v>
+        <v>-1.5792</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8891</v>
+        <v>0.861</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0351</v>
+        <v>0.4288</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.854</v>
+        <v>0.4323</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.986</v>
+        <v>-1.8098</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2046</v>
+        <v>0.106</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7814</v>
+        <v>-1.9158</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1229</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4867</v>
+        <v>-0.3106</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6721</v>
+        <v>-0.3615</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1854</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.093</v>
+        <v>-2.9847</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0682</v>
+        <v>0.0065</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0248</v>
+        <v>-2.9912</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1388</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2041</v>
+        <v>-1.0958</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>-0.8962</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6778999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3975</v>
+        <v>-5.1496</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.654</v>
+        <v>-2.4732</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7436</v>
+        <v>-2.6763</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7626</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7045</v>
+        <v>-1.4565</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7073</v>
+        <v>-0.5265</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9972</v>
+        <v>-0.93</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5963</v>
+        <v>-6.4039</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0676</v>
+        <v>-2.5994</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5287</v>
+        <v>-3.8044</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.5089</v>
+        <v>-2.0797</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.1224</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.5774</v>
+        <v>-1.9573</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3932</v>
+        <v>-0.0678</v>
       </c>
       <c r="K12" t="n">
-        <v>0.605</v>
+        <v>-0.215</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.9982</v>
+        <v>0.1472</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1157</v>
+        <v>-2.012</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5365</v>
+        <v>0.0926</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5792</v>
+        <v>-2.1045</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.7185</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1142</v>
+        <v>-0.2122</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1964</v>
+        <v>-0.5063</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.933</v>
+        <v>-1.7501</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1444</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.0319</v>
+        <v>-6.7254</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0594</v>
+        <v>-2.9615</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9725</v>
+        <v>-3.7639</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0797</v>
+        <v>-4.5089</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1224</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9573</v>
+        <v>-4.5774</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0678</v>
+        <v>-2.3932</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.215</v>
+        <v>0.605</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1472</v>
+        <v>-2.9982</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.012</v>
+        <v>-2.1157</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0926</v>
+        <v>-0.5365</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1045</v>
+        <v>-1.5792</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3465</v>
+        <v>-0.2113</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>0.2203</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6743</v>
+        <v>-0.4316</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7501</v>
+        <v>-2.933</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7501</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.3221</v>
+        <v>-16.8286</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3592999999999988</v>
+        <v>1.1343</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.963</v>
+        <v>-17.9626</v>
       </c>
       <c r="G14" t="n">
         <v>-11.8115</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1455</v>
+        <v>3.145500000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-14.9568</v>
@@ -1537,7 +1537,7 @@
         <v>-21.0617</v>
       </c>
       <c r="P14" t="n">
-        <v>4.6392</v>
+        <v>4.639199999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.7575</v>
@@ -1546,10 +1546,10 @@
         <v>17.3965</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.466399999999999</v>
+        <v>-4.972899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.9114</v>
+        <v>-3.4179</v>
       </c>
       <c r="U14" t="n">
         <v>-1.555</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.4458</v>
+        <v>9.405200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.220800000000001</v>
+        <v>8.810600000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.225</v>
+        <v>0.5946</v>
       </c>
       <c r="G15" t="n">
         <v>7.4313</v>
@@ -1624,13 +1624,13 @@
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4494</v>
+        <v>0.51</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2671</v>
+        <v>0.3227</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1823</v>
+        <v>0.1874</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3441</v>
+        <v>4.8324</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2454</v>
+        <v>4.5992</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0988</v>
+        <v>0.2332</v>
       </c>
       <c r="G16" t="n">
         <v>1.9687</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2328</v>
+        <v>0.2555</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3567</v>
+        <v>0.4911</v>
       </c>
       <c r="V16" t="n">
         <v>2.1444</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1421</v>
+        <v>3.6737</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6384</v>
+        <v>3.8952</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5037</v>
+        <v>-0.2216</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9782999999999999</v>
+        <v>3.542</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3735</v>
+        <v>0.3567</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3519</v>
+        <v>3.1853</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9106</v>
+        <v>4.046</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0273</v>
+        <v>0.9579</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8833</v>
+        <v>3.0881</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0678</v>
+        <v>-0.5039</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4008</v>
+        <v>-0.6012</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4685</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6302</v>
+        <v>1.312</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.2047</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8123</v>
+        <v>1.1073</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>2.428</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5064</v>
+        <v>3.6037</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1184</v>
+        <v>1.4025</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6121</v>
+        <v>2.2012</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0209</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2784</v>
+        <v>-0.3735</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2575</v>
+        <v>1.3519</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8677</v>
+        <v>0.9106</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6469</v>
+        <v>0.0273</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2208</v>
+        <v>0.8833</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8468</v>
+        <v>0.0678</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3684</v>
+        <v>-0.4008</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4783</v>
+        <v>0.4685</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1813</v>
+        <v>1.0919</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3383</v>
+        <v>0.5821</v>
       </c>
       <c r="U18" t="n">
-        <v>0.843</v>
+        <v>0.5098</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2355</v>
+        <v>2.8665</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4234</v>
+        <v>3.6466</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.188</v>
+        <v>-0.7801</v>
       </c>
       <c r="G19" t="n">
-        <v>3.542</v>
+        <v>1.0209</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3567</v>
+        <v>1.2784</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1853</v>
+        <v>-0.2575</v>
       </c>
       <c r="J19" t="n">
-        <v>4.046</v>
+        <v>1.8677</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9579</v>
+        <v>1.6469</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0881</v>
+        <v>0.2208</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5039</v>
+        <v>-0.8468</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6012</v>
+        <v>-0.3684</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09719999999999999</v>
+        <v>-0.4783</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8738</v>
+        <v>0.5414</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2671</v>
+        <v>-0.1336</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1409</v>
+        <v>0.675</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2525</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>2.428</v>
+        <v>2.1444</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5395</v>
+        <v>1.5731</v>
       </c>
       <c r="E20" t="n">
         <v>1.3546</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1849</v>
+        <v>0.2185</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9491000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6278</v>
+        <v>0.6614</v>
       </c>
       <c r="T20" t="n">
         <v>0.3541</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2737</v>
+        <v>0.3073</v>
       </c>
       <c r="V20" t="n">
         <v>1.8608</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8708</v>
+        <v>1.1904</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8197</v>
+        <v>2.9377</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9489</v>
+        <v>-1.7473</v>
       </c>
       <c r="G21" t="n">
         <v>0.8778</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.007</v>
+        <v>0.3126</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1344</v>
+        <v>0.3361</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5177</v>
+        <v>-0.299</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6867</v>
+        <v>-0.5688</v>
       </c>
       <c r="F22" t="n">
-        <v>0.169</v>
+        <v>0.2698</v>
       </c>
       <c r="G22" t="n">
         <v>2.1755</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4485</v>
+        <v>0.6673</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.275</v>
+        <v>-0.1571</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7235</v>
+        <v>0.8244</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7501</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9268</v>
+        <v>-2.1291</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5397</v>
+        <v>-3.7756</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6129</v>
+        <v>1.6465</v>
       </c>
       <c r="G23" t="n">
         <v>-0.872</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0328</v>
+        <v>0.8305</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7433</v>
+        <v>0.5074</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2895</v>
+        <v>0.3231</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.401</v>
+        <v>-3.1359</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1762</v>
+        <v>-1.8093</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2249</v>
+        <v>-1.3266</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8891</v>
+        <v>-1.4729</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7515</v>
+        <v>0.1465</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1376</v>
+        <v>-1.6194</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4991</v>
+        <v>0.5925</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5727</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0736</v>
+        <v>-0.2477</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.39</v>
+        <v>-2.0655</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1788</v>
+        <v>-0.6938</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2112</v>
+        <v>-1.3717</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8556</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4132</v>
+        <v>-0.2713</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5702</v>
+        <v>-0.0824</v>
       </c>
       <c r="U24" t="n">
-        <v>0.843</v>
+        <v>-0.1889</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9165</v>
+        <v>-3.259</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4555</v>
+        <v>-2.53</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.461</v>
+        <v>-0.729</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4729</v>
+        <v>-2.8891</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1465</v>
+        <v>-1.7515</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6194</v>
+        <v>-1.1376</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5925</v>
+        <v>-1.4991</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8401999999999999</v>
+        <v>-1.5727</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2477</v>
+        <v>0.0736</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0655</v>
+        <v>-1.39</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6938</v>
+        <v>-0.1788</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.3717</v>
+        <v>-1.2112</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3917</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0518</v>
+        <v>0.5553</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2715</v>
+        <v>0.2164</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3233</v>
+        <v>0.3389</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>18.3222</v>
+        <v>18.322</v>
       </c>
       <c r="E26" t="n">
-        <v>17.9626</v>
+        <v>17.9627</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3594000000000002</v>
+        <v>0.3592000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>11.8114</v>
@@ -2485,10 +2485,10 @@
         <v>6.4666</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5552</v>
+        <v>1.5551</v>
       </c>
       <c r="U26" t="n">
-        <v>4.9114</v>
+        <v>4.911499999999999</v>
       </c>
       <c r="V26" t="n">
         <v>4.6831</v>
